--- a/TestComponents/TestSets/Residues/FieldConfigs.xlsx
+++ b/TestComponents/TestSets/Residues/FieldConfigs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\FieldNBalance\TestComponents\TestSets\Residues\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14826755-3A35-4431-B953-CE9B7172C8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8055744A-37A1-44D5-8A68-B4122EAF59F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D0D9F3F3-C1B3-4B79-AF5D-93A117BC34BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0D9F3F3-C1B3-4B79-AF5D-93A117BC34BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="77">
   <si>
     <t>StovN0.5High</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>Top30cm</t>
+  </si>
+  <si>
+    <t>FinalFertDate</t>
   </si>
 </sst>
 </file>
@@ -693,14 +696,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67FC6C2-7F6C-4E8B-9465-EDB17589DEC5}">
-  <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>62</v>
       </c>
@@ -735,7 +738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>63</v>
       </c>
@@ -773,7 +776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" t="s">
         <v>10</v>
@@ -809,7 +812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" t="s">
         <v>70</v>
@@ -845,7 +848,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
       <c r="B5" t="s">
         <v>72</v>
@@ -881,7 +884,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" t="s">
         <v>73</v>
@@ -917,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" t="s">
         <v>11</v>
@@ -953,7 +956,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" t="s">
         <v>12</v>
@@ -989,7 +992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" t="s">
         <v>13</v>
@@ -1025,7 +1028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" t="s">
         <v>14</v>
@@ -1061,7 +1064,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" t="s">
         <v>16</v>
@@ -1097,7 +1100,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" t="s">
         <v>17</v>
@@ -1133,120 +1136,90 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>13</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>13</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>13</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>13</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>6</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>6</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>6</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>6</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1279,372 +1252,372 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="D18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="E18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="F18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="G18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="H18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="I18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="J18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="K18" s="5">
-        <v>44831</v>
-      </c>
-      <c r="L18" s="5">
-        <v>44831</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>13</v>
+      </c>
+      <c r="I18">
+        <v>13</v>
+      </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
+      <c r="K18">
+        <v>13</v>
+      </c>
+      <c r="L18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="D19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="E19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="F19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="G19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="H19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="I19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="J19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="K19" s="5">
+        <v>44831</v>
+      </c>
+      <c r="L19" s="5">
+        <v>44831</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="D20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="E20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="F20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="G20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="H20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="I20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="J20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="K20" s="5">
-        <v>44951</v>
-      </c>
-      <c r="L20" s="5">
-        <v>44951</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" t="s">
-        <v>33</v>
-      </c>
-      <c r="L21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="D21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="E21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="F21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="G21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="H21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="I21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="J21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="K21" s="5">
+        <v>44951</v>
+      </c>
+      <c r="L21" s="5">
+        <v>44951</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>23</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>23</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>23</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H25" t="s">
         <v>23</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I25" t="s">
         <v>23</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J25" t="s">
         <v>23</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K25" t="s">
         <v>23</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+    <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C26" s="3">
         <v>8</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D26" s="3">
         <v>8</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E26" s="3">
         <v>8</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F26" s="3">
         <v>8</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G26" s="3">
         <v>8</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H26" s="3">
         <v>8</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I26" s="3">
         <v>8</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J26" s="3">
         <v>8</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K26" s="3">
         <v>8</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L26" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1677,372 +1650,372 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="D29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="E29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="F29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="G29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="H29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="I29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="J29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="K29" s="5">
-        <v>45026</v>
-      </c>
-      <c r="L29" s="5">
-        <v>45026</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>15</v>
+      </c>
+      <c r="I29">
+        <v>15</v>
+      </c>
+      <c r="J29">
+        <v>15</v>
+      </c>
+      <c r="K29">
+        <v>15</v>
+      </c>
+      <c r="L29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" t="s">
-        <v>30</v>
-      </c>
-      <c r="G30" t="s">
-        <v>30</v>
-      </c>
-      <c r="H30" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" t="s">
-        <v>30</v>
-      </c>
-      <c r="J30" t="s">
-        <v>30</v>
-      </c>
-      <c r="K30" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="C30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="D30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="E30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="F30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="G30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="H30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="I30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="J30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="K30" s="5">
+        <v>45026</v>
+      </c>
+      <c r="L30" s="5">
+        <v>45026</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="D31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="E31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="F31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="G31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="H31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="I31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="J31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="K31" s="5">
-        <v>45142</v>
-      </c>
-      <c r="L31" s="5">
-        <v>45142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" t="s">
-        <v>33</v>
-      </c>
-      <c r="K32" t="s">
-        <v>33</v>
-      </c>
-      <c r="L32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="C32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="D32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="E32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="F32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="G32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="H32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="I32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="J32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="K32" s="5">
+        <v>45142</v>
+      </c>
+      <c r="L32" s="5">
+        <v>45142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" t="s">
+        <v>35</v>
+      </c>
+      <c r="J34" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34" t="s">
+        <v>35</v>
+      </c>
+      <c r="L34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" t="s">
         <v>47</v>
       </c>
-      <c r="C34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s">
-        <v>37</v>
-      </c>
-      <c r="I34" t="s">
-        <v>37</v>
-      </c>
-      <c r="J34" t="s">
-        <v>37</v>
-      </c>
-      <c r="K34" t="s">
-        <v>37</v>
-      </c>
-      <c r="L34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8"/>
-      <c r="B35" s="1" t="s">
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" t="s">
+        <v>37</v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" t="s">
+        <v>37</v>
+      </c>
+      <c r="K35" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>69</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>10</v>
       </c>
-      <c r="D36">
+      <c r="D37">
         <v>10</v>
       </c>
-      <c r="E36">
+      <c r="E37">
         <v>10</v>
       </c>
-      <c r="F36">
+      <c r="F37">
         <v>10</v>
       </c>
-      <c r="G36">
+      <c r="G37">
         <v>10</v>
       </c>
-      <c r="H36">
+      <c r="H37">
         <v>10</v>
       </c>
-      <c r="I36">
+      <c r="I37">
         <v>10</v>
       </c>
-      <c r="J36">
+      <c r="J37">
         <v>10</v>
       </c>
-      <c r="K36">
+      <c r="K37">
         <v>10</v>
       </c>
-      <c r="L36">
+      <c r="L37">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2075,10 +2048,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2111,228 +2084,264 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="D40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="E40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="F40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="G40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="H40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="I40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="J40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="K40" s="5">
-        <v>45170</v>
-      </c>
-      <c r="L40" s="5">
-        <v>45170</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41" t="s">
-        <v>30</v>
-      </c>
-      <c r="J41" t="s">
-        <v>30</v>
-      </c>
-      <c r="K41" t="s">
-        <v>30</v>
-      </c>
-      <c r="L41" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="C41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="D41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="E41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="F41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="G41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="H41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="I41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="J41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="K41" s="5">
+        <v>45170</v>
+      </c>
+      <c r="L41" s="5">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="D42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="E42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="F42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="G42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="H42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="I42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="J42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="K42" s="5">
-        <v>45200</v>
-      </c>
-      <c r="L42" s="5">
-        <v>45200</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I43" t="s">
-        <v>57</v>
-      </c>
-      <c r="J43" t="s">
-        <v>57</v>
-      </c>
-      <c r="K43" t="s">
-        <v>57</v>
-      </c>
-      <c r="L43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="C43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="D43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="E43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="F43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="G43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="H43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="I43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="J43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="K43" s="5">
+        <v>45200</v>
+      </c>
+      <c r="L43" s="5">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H44" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" t="s">
+        <v>57</v>
+      </c>
+      <c r="J44" t="s">
+        <v>57</v>
+      </c>
+      <c r="K44" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" t="s">
         <v>58</v>
       </c>
-      <c r="C44" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" t="s">
-        <v>35</v>
-      </c>
-      <c r="F44" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I44" t="s">
-        <v>35</v>
-      </c>
-      <c r="J44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" t="s">
-        <v>35</v>
-      </c>
-      <c r="L44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="9"/>
-      <c r="B45" s="1" t="s">
+      <c r="C45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" t="s">
+        <v>35</v>
+      </c>
+      <c r="L45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L45" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A14:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A15:A25"/>
+    <mergeCell ref="A26:A36"/>
+    <mergeCell ref="A37:A46"/>
+    <mergeCell ref="A2:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
